--- a/Remote/ug16/Données/03/dist_liens.xlsx
+++ b/Remote/ug16/Données/03/dist_liens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mickaël\Documents\GitHub\ductaironline\Remote\ug16\Données\04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0727C365-D02A-4EC4-95ED-1066A22817E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D3A255-F0E0-401F-8AD1-5B5EF80B3BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10E80606-BDFD-48EA-859F-8B282D217FD1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3620" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="280">
   <si>
     <t>id</t>
   </si>
@@ -874,6 +874,12 @@
   <si>
     <t>Cinconnu</t>
   </si>
+  <si>
+    <t>Ø1</t>
+  </si>
+  <si>
+    <t>Ø2</t>
+  </si>
 </sst>
 </file>
 
@@ -42508,7 +42514,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -43234,10 +43240,10 @@
         <v>31</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L170" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M170" s="2" t="s">
         <v>34</v>
@@ -43479,10 +43485,10 @@
         <v>31</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L171" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M171" s="2" t="s">
         <v>34</v>
@@ -43724,10 +43730,10 @@
         <v>31</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L172" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L172" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M172" s="2" t="s">
         <v>34</v>
@@ -43969,10 +43975,10 @@
         <v>31</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L173" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M173" s="2" t="s">
         <v>34</v>
@@ -44214,10 +44220,10 @@
         <v>31</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L174" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M174" s="2" t="s">
         <v>34</v>
@@ -44459,10 +44465,10 @@
         <v>31</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L175" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M175" s="2" t="s">
         <v>34</v>
@@ -44704,10 +44710,10 @@
         <v>31</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L176" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M176" s="2" t="s">
         <v>34</v>
@@ -44949,10 +44955,10 @@
         <v>31</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L177" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M177" s="2" t="s">
         <v>34</v>
@@ -45194,10 +45200,10 @@
         <v>31</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L178" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M178" s="2" t="s">
         <v>34</v>
@@ -45439,10 +45445,10 @@
         <v>31</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L179" s="2">
-        <v>0</v>
+        <v>278</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M179" s="2" t="s">
         <v>34</v>
